--- a/exports/trend_1d/BAJAJHLDNG_full_report.xlsx
+++ b/exports/trend_1d/BAJAJHLDNG_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.15</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42068</v>
+        <v>42072</v>
       </c>
       <c r="H2" t="n">
-        <v>1395.5</v>
+        <v>1328.8</v>
       </c>
       <c r="I2" t="n">
         <v>1348.78</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.97</v>
+        <v>-9.51</v>
       </c>
       <c r="L2" t="n">
         <v>10.92</v>
@@ -555,7 +578,7 @@
         <v>0.89</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>4.78</v>
       </c>
       <c r="O2" t="n">
         <v>-1.85</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42150</v>
+        <v>42151</v>
       </c>
       <c r="H3" t="n">
-        <v>1307.34</v>
+        <v>1331.95</v>
       </c>
       <c r="I3" t="n">
         <v>1328.132543187351</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K3" t="n">
-        <v>1.61</v>
+        <v>-0.24</v>
       </c>
       <c r="L3" t="n">
         <v>5.13</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.52</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42206</v>
+        <v>42207</v>
       </c>
       <c r="H4" t="n">
-        <v>1392.8</v>
+        <v>1379.45</v>
       </c>
       <c r="I4" t="n">
         <v>1388.248430209017</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>4.57</v>
+        <v>3.57</v>
       </c>
       <c r="L4" t="n">
         <v>3.15</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.68</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H5" t="n">
-        <v>1477.55</v>
+        <v>1503.15</v>
       </c>
       <c r="I5" t="n">
         <v>1499.224698385302</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.11</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>8.74</v>
+        <v>10.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.36</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.9</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42248</v>
+        <v>42249</v>
       </c>
       <c r="H6" t="n">
-        <v>1613.65</v>
+        <v>1556.9</v>
       </c>
       <c r="I6" t="n">
         <v>1560.027811200563</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>7.35</v>
+        <v>3.58</v>
       </c>
       <c r="L6" t="n">
         <v>1.6</v>
@@ -783,7 +854,7 @@
         <v>2.37</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>3.52</v>
       </c>
       <c r="O6" t="n">
         <v>1.73</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>12.67</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42303</v>
+        <v>42304</v>
       </c>
       <c r="H7" t="n">
-        <v>1625.2</v>
+        <v>1667.8</v>
       </c>
       <c r="I7" t="n">
         <v>1664.980573103704</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.39</v>
+        <v>-7.12</v>
       </c>
       <c r="L7" t="n">
-        <v>6.64</v>
+        <v>7.91</v>
       </c>
       <c r="M7" t="n">
         <v>2.28</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.35</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42349</v>
+        <v>42352</v>
       </c>
       <c r="H8" t="n">
-        <v>1675.15</v>
+        <v>1610.4</v>
       </c>
       <c r="I8" t="n">
         <v>1646.125476042542</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>0.44</v>
+        <v>-3.44</v>
       </c>
       <c r="L8" t="n">
-        <v>2.27</v>
+        <v>3.95</v>
       </c>
       <c r="M8" t="n">
         <v>1.23</v>
       </c>
       <c r="N8" t="n">
-        <v>2.09</v>
+        <v>3.87</v>
       </c>
       <c r="O8" t="n">
         <v>2.62</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.92</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42502</v>
+        <v>42503</v>
       </c>
       <c r="H9" t="n">
-        <v>1511.4</v>
+        <v>1520.2</v>
       </c>
       <c r="I9" t="n">
         <v>1512.171268288134</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K9" t="n">
-        <v>6.15</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
         <v>8.48</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.49</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H10" t="n">
-        <v>2011.55</v>
+        <v>1975.6</v>
       </c>
       <c r="I10" t="n">
         <v>1994.720346849852</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K10" t="n">
-        <v>32.32</v>
+        <v>29.96</v>
       </c>
       <c r="L10" t="n">
         <v>3.4</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>16.38</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42765</v>
+        <v>42766</v>
       </c>
       <c r="H11" t="n">
-        <v>1933.85</v>
+        <v>1999.45</v>
       </c>
       <c r="I11" t="n">
         <v>1946.700999299477</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" t="n">
-        <v>2.11</v>
+        <v>-1.21</v>
       </c>
       <c r="L11" t="n">
         <v>9.32</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.7</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H12" t="n">
-        <v>2095.65</v>
+        <v>2049.1</v>
       </c>
       <c r="I12" t="n">
         <v>2077.23163469136</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K12" t="n">
-        <v>4.81</v>
+        <v>2.48</v>
       </c>
       <c r="L12" t="n">
         <v>3.04</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.83</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42928</v>
+        <v>42929</v>
       </c>
       <c r="H13" t="n">
-        <v>2163.7</v>
+        <v>2195.7</v>
       </c>
       <c r="I13" t="n">
         <v>2185.454170769322</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.59</v>
+        <v>-7.15</v>
       </c>
       <c r="L13" t="n">
-        <v>6.14</v>
+        <v>7.66</v>
       </c>
       <c r="M13" t="n">
         <v>2.92</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H14" t="n">
-        <v>2770.55</v>
+        <v>2724.7</v>
       </c>
       <c r="I14" t="n">
         <v>2766.806374350291</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K14" t="n">
-        <v>26.18</v>
+        <v>24.09</v>
       </c>
       <c r="L14" t="n">
         <v>1.63</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43217</v>
+        <v>43220</v>
       </c>
       <c r="H15" t="n">
-        <v>2645.95</v>
+        <v>2705.65</v>
       </c>
       <c r="I15" t="n">
         <v>2698.957272313806</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K15" t="n">
-        <v>2.89</v>
+        <v>0.7</v>
       </c>
       <c r="L15" t="n">
         <v>8.449999999999999</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43278</v>
+        <v>43279</v>
       </c>
       <c r="H16" t="n">
-        <v>2973.1</v>
+        <v>2883.3</v>
       </c>
       <c r="I16" t="n">
         <v>2930.825631285603</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K16" t="n">
-        <v>9.880000000000001</v>
+        <v>6.57</v>
       </c>
       <c r="L16" t="n">
         <v>4.94</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.71</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H17" t="n">
-        <v>2925.25</v>
+        <v>2954.5</v>
       </c>
       <c r="I17" t="n">
         <v>2935.972622977571</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.45</v>
+        <v>-2.47</v>
       </c>
       <c r="L17" t="n">
         <v>11.37</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.59</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H18" t="n">
-        <v>2853.5</v>
+        <v>2844.9</v>
       </c>
       <c r="I18" t="n">
         <v>2849.164386551998</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.42</v>
+        <v>-3.71</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.41</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43502</v>
+        <v>43503</v>
       </c>
       <c r="H19" t="n">
-        <v>2994.25</v>
+        <v>3116.85</v>
       </c>
       <c r="I19" t="n">
         <v>3027.317458594659</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.25</v>
+        <v>-9.56</v>
       </c>
       <c r="L19" t="n">
-        <v>8.449999999999999</v>
+        <v>11.78</v>
       </c>
       <c r="M19" t="n">
         <v>0.1</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.42</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H20" t="n">
-        <v>3268.6</v>
+        <v>3086</v>
       </c>
       <c r="I20" t="n">
         <v>3145.82107357589</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K20" t="n">
-        <v>4.87</v>
+        <v>-0.99</v>
       </c>
       <c r="L20" t="n">
-        <v>4.18</v>
+        <v>4.39</v>
       </c>
       <c r="M20" t="n">
         <v>3.63</v>
       </c>
       <c r="N20" t="n">
-        <v>4.93</v>
+        <v>5.59</v>
       </c>
       <c r="O20" t="n">
         <v>4.09</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>10.72</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H21" t="n">
-        <v>3281.7</v>
+        <v>3325.75</v>
       </c>
       <c r="I21" t="n">
         <v>3312.777370421822</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.34</v>
+        <v>-7.77</v>
       </c>
       <c r="L21" t="n">
-        <v>7.26</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.84</v>
+        <v>1.56</v>
       </c>
       <c r="N21" t="n">
         <v>3.84</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.44</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43665</v>
+        <v>43668</v>
       </c>
       <c r="H22" t="n">
-        <v>3500.05</v>
+        <v>3431</v>
       </c>
       <c r="I22" t="n">
         <v>3470.522444062913</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K22" t="n">
-        <v>5.24</v>
+        <v>3.16</v>
       </c>
       <c r="L22" t="n">
         <v>2.25</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.68</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H23" t="n">
-        <v>3233.95</v>
+        <v>3537.55</v>
       </c>
       <c r="I23" t="n">
         <v>3416.819245949406</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K23" t="n">
-        <v>5.74</v>
+        <v>-3.11</v>
       </c>
       <c r="L23" t="n">
-        <v>4.78</v>
+        <v>7.29</v>
       </c>
       <c r="M23" t="n">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="N23" t="n">
-        <v>4.69</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-1.97</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43798</v>
+        <v>43801</v>
       </c>
       <c r="H24" t="n">
-        <v>3564.35</v>
+        <v>3517.45</v>
       </c>
       <c r="I24" t="n">
         <v>3550.251827323623</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K24" t="n">
-        <v>0.76</v>
+        <v>-0.57</v>
       </c>
       <c r="L24" t="n">
         <v>6.57</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.58</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H25" t="n">
-        <v>3454.3</v>
+        <v>3525.65</v>
       </c>
       <c r="I25" t="n">
         <v>3494.685359511502</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K25" t="n">
-        <v>1.8</v>
+        <v>-0.23</v>
       </c>
       <c r="L25" t="n">
         <v>2.06</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.35</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H26" t="n">
-        <v>3642.25</v>
+        <v>3483</v>
       </c>
       <c r="I26" t="n">
         <v>3506.491967857882</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>3.31</v>
+        <v>-1.21</v>
       </c>
       <c r="L26" t="n">
         <v>2.51</v>
@@ -1923,7 +2234,7 @@
         <v>0.26</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>4.37</v>
       </c>
       <c r="O26" t="n">
         <v>2.07</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.38</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H27" t="n">
-        <v>2066</v>
+        <v>2188.2</v>
       </c>
       <c r="I27" t="n">
         <v>2134.772902665259</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>40.68</v>
+        <v>37.17</v>
       </c>
       <c r="L27" t="n">
         <v>4.74</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.71</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44078</v>
+        <v>44081</v>
       </c>
       <c r="H28" t="n">
-        <v>2590.5</v>
+        <v>2485.05</v>
       </c>
       <c r="I28" t="n">
         <v>2584.348961715002</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K28" t="n">
-        <v>18.38</v>
+        <v>13.57</v>
       </c>
       <c r="L28" t="n">
         <v>8.050000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.83</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44141</v>
+        <v>44144</v>
       </c>
       <c r="H29" t="n">
-        <v>2426.9</v>
+        <v>2445.9</v>
       </c>
       <c r="I29" t="n">
         <v>2441.701032354347</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K29" t="n">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="L29" t="n">
         <v>5.83</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.42</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44273</v>
+        <v>44274</v>
       </c>
       <c r="H30" t="n">
-        <v>3537.75</v>
+        <v>3429</v>
       </c>
       <c r="I30" t="n">
         <v>3439.50121296833</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K30" t="n">
-        <v>44.64</v>
+        <v>40.19</v>
       </c>
       <c r="L30" t="n">
         <v>1.41</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.74</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H31" t="n">
-        <v>3556.85</v>
+        <v>3599.95</v>
       </c>
       <c r="I31" t="n">
         <v>3595.056875358718</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.73</v>
+        <v>-4.99</v>
       </c>
       <c r="L31" t="n">
         <v>6.82</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H32" t="n">
-        <v>5036.4</v>
+        <v>4991.85</v>
       </c>
       <c r="I32" t="n">
         <v>5017.033066413401</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K32" t="n">
-        <v>39.9</v>
+        <v>38.66</v>
       </c>
       <c r="L32" t="n">
         <v>4.14</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.88</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H33" t="n">
-        <v>5011.05</v>
+        <v>5398.85</v>
       </c>
       <c r="I33" t="n">
         <v>5352.310070039912</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.38</v>
+        <v>-8.15</v>
       </c>
       <c r="L33" t="n">
         <v>11.98</v>
@@ -2322,7 +2717,7 @@
         <v>5.17</v>
       </c>
       <c r="N33" t="n">
-        <v>5.29</v>
+        <v>7.74</v>
       </c>
       <c r="O33" t="n">
         <v>-0.88</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.89</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44664</v>
+        <v>44669</v>
       </c>
       <c r="H34" t="n">
-        <v>5517.05</v>
+        <v>5204.4</v>
       </c>
       <c r="I34" t="n">
         <v>5414.735946050818</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>2.19</v>
+        <v>-3.6</v>
       </c>
       <c r="L34" t="n">
         <v>6.83</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>20.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44753</v>
+        <v>44754</v>
       </c>
       <c r="H35" t="n">
-        <v>4904.6</v>
+        <v>4942.55</v>
       </c>
       <c r="I35" t="n">
         <v>4942.427007183875</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K35" t="n">
-        <v>5.76</v>
+        <v>5.03</v>
       </c>
       <c r="L35" t="n">
         <v>7.89</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.15</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44889</v>
+        <v>44890</v>
       </c>
       <c r="H36" t="n">
-        <v>6521.25</v>
+        <v>6371.8</v>
       </c>
       <c r="I36" t="n">
         <v>6416.463236059627</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K36" t="n">
-        <v>31.94</v>
+        <v>28.92</v>
       </c>
       <c r="L36" t="n">
         <v>4.48</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>9.84</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H37" t="n">
-        <v>5883.95</v>
+        <v>6082.2</v>
       </c>
       <c r="I37" t="n">
         <v>6051.774174909469</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K37" t="n">
-        <v>7.66</v>
+        <v>4.55</v>
       </c>
       <c r="L37" t="n">
         <v>3.96</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N37" t="n">
         <v>4.5</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.82</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H38" t="n">
-        <v>5920.1</v>
+        <v>5819.5</v>
       </c>
       <c r="I38" t="n">
         <v>5840.461256780114</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.67</v>
+        <v>-4.32</v>
       </c>
       <c r="L38" t="n">
-        <v>4.31</v>
+        <v>5.13</v>
       </c>
       <c r="M38" t="n">
         <v>0.8100000000000001</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45035</v>
+        <v>45036</v>
       </c>
       <c r="H39" t="n">
-        <v>6315.55</v>
+        <v>6401.25</v>
       </c>
       <c r="I39" t="n">
         <v>6369.268978328827</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.52</v>
+        <v>-10</v>
       </c>
       <c r="L39" t="n">
         <v>14.29</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.69</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="H40" t="n">
-        <v>6632.7</v>
+        <v>6451.85</v>
       </c>
       <c r="I40" t="n">
         <v>6465.211723732264</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" t="n">
-        <v>3.62</v>
+        <v>0.79</v>
       </c>
       <c r="L40" t="n">
         <v>1.43</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45069</v>
+        <v>45070</v>
       </c>
       <c r="H41" t="n">
-        <v>6641.4</v>
+        <v>6934.45</v>
       </c>
       <c r="I41" t="n">
         <v>6793.706570203001</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.94</v>
+        <v>-7.48</v>
       </c>
       <c r="L41" t="n">
-        <v>3.54</v>
+        <v>7.97</v>
       </c>
       <c r="M41" t="n">
         <v>0.75</v>
       </c>
       <c r="N41" t="n">
-        <v>2.99</v>
+        <v>4.41</v>
       </c>
       <c r="O41" t="n">
         <v>-2.73</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.1</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H42" t="n">
-        <v>7147</v>
+        <v>6943.2</v>
       </c>
       <c r="I42" t="n">
         <v>7092.918355149135</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K42" t="n">
-        <v>3.07</v>
+        <v>0.13</v>
       </c>
       <c r="L42" t="n">
         <v>4.66</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.74</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H43" t="n">
-        <v>7138.4</v>
+        <v>7347.8</v>
       </c>
       <c r="I43" t="n">
         <v>7236.743499399636</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.81</v>
+        <v>-5.83</v>
       </c>
       <c r="L43" t="n">
         <v>7.93</v>
@@ -2892,7 +3407,7 @@
         <v>1.5</v>
       </c>
       <c r="N43" t="n">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="O43" t="n">
         <v>-2.85</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>7.4</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45364</v>
+        <v>45365</v>
       </c>
       <c r="H44" t="n">
-        <v>8369</v>
+        <v>8231</v>
       </c>
       <c r="I44" t="n">
         <v>8235.075349038138</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K44" t="n">
-        <v>13.9</v>
+        <v>12.02</v>
       </c>
       <c r="L44" t="n">
         <v>3.25</v>
       </c>
       <c r="M44" t="n">
-        <v>1.18</v>
+        <v>1.72</v>
       </c>
       <c r="N44" t="n">
         <v>4.27</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H45" t="n">
-        <v>8350</v>
+        <v>8383.549999999999</v>
       </c>
       <c r="I45" t="n">
         <v>8364.04775089286</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.45</v>
+        <v>-1.85</v>
       </c>
       <c r="L45" t="n">
         <v>3.39</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.73</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45439</v>
+        <v>45440</v>
       </c>
       <c r="H46" t="n">
-        <v>7988.3</v>
+        <v>7852.6</v>
       </c>
       <c r="I46" t="n">
         <v>7942.703930317278</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.71</v>
+        <v>-6.33</v>
       </c>
       <c r="L46" t="n">
-        <v>4.99</v>
+        <v>6.66</v>
       </c>
       <c r="M46" t="n">
         <v>0.39</v>
       </c>
       <c r="N46" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O46" t="n">
         <v>0.4</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.54</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="H47" t="n">
-        <v>8130.3</v>
+        <v>8377.6</v>
       </c>
       <c r="I47" t="n">
         <v>8247.48527892828</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.54</v>
+        <v>-6.69</v>
       </c>
       <c r="L47" t="n">
-        <v>3.72</v>
+        <v>7.16</v>
       </c>
       <c r="M47" t="n">
         <v>2.21</v>
       </c>
       <c r="N47" t="n">
-        <v>2.47</v>
+        <v>3.04</v>
       </c>
       <c r="O47" t="n">
         <v>-1.7</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.98</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="H48" t="n">
-        <v>10216.85</v>
+        <v>10117.3</v>
       </c>
       <c r="I48" t="n">
         <v>10139.25477915574</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K48" t="n">
-        <v>21.95</v>
+        <v>20.77</v>
       </c>
       <c r="L48" t="n">
         <v>2.56</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>10.44</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="H49" t="n">
-        <v>10675.85</v>
+        <v>11122</v>
       </c>
       <c r="I49" t="n">
         <v>11076.02010732168</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.52</v>
+        <v>-9.93</v>
       </c>
       <c r="L49" t="n">
-        <v>10.25</v>
+        <v>11.14</v>
       </c>
       <c r="M49" t="n">
         <v>1.51</v>
       </c>
       <c r="N49" t="n">
-        <v>3.46</v>
+        <v>4.18</v>
       </c>
       <c r="O49" t="n">
         <v>-0.97</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>10.61</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H50" t="n">
-        <v>10827.85</v>
+        <v>10314.8</v>
       </c>
       <c r="I50" t="n">
         <v>10560.57414366089</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.64</v>
+        <v>-7.26</v>
       </c>
       <c r="L50" t="n">
-        <v>4.23</v>
+        <v>7.88</v>
       </c>
       <c r="M50" t="n">
         <v>1.42</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>17.74</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45689</v>
+        <v>45691</v>
       </c>
       <c r="H51" t="n">
-        <v>11754</v>
+        <v>12205</v>
       </c>
       <c r="I51" t="n">
         <v>12076.11927649383</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.95</v>
+        <v>-18.33</v>
       </c>
       <c r="L51" t="n">
-        <v>15.05</v>
+        <v>20.4</v>
       </c>
       <c r="M51" t="n">
         <v>2.3</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>12.86</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H52" t="n">
-        <v>11506.9</v>
+        <v>10779.6</v>
       </c>
       <c r="I52" t="n">
         <v>11384.09786786037</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.72</v>
+        <v>-11.68</v>
       </c>
       <c r="L52" t="n">
-        <v>9.199999999999999</v>
+        <v>14.79</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>4.5</v>
+        <v>6.32</v>
       </c>
       <c r="O52" t="n">
         <v>3.84</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>13.58</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H53" t="n">
-        <v>12207</v>
+        <v>12324</v>
       </c>
       <c r="I53" t="n">
         <v>12243.88633625713</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-13.24</v>
+        <v>-14.33</v>
       </c>
       <c r="L53" t="n">
-        <v>13.62</v>
+        <v>15.37</v>
       </c>
       <c r="M53" t="n">
         <v>4.36</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.27</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="H54" t="n">
-        <v>13265</v>
+        <v>12997</v>
       </c>
       <c r="I54" t="n">
         <v>13183.64514245798</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K54" t="n">
-        <v>7.64</v>
+        <v>5.46</v>
       </c>
       <c r="L54" t="n">
         <v>9.52</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>11.23</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H55" t="n">
-        <v>12732</v>
+        <v>13144</v>
       </c>
       <c r="I55" t="n">
         <v>12954.29204157594</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K55" t="n">
-        <v>2.04</v>
+        <v>-1.13</v>
       </c>
       <c r="L55" t="n">
         <v>6.79</v>
@@ -3576,7 +4235,7 @@
         <v>1.54</v>
       </c>
       <c r="N55" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="O55" t="n">
         <v>-2.02</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.91</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="H56" t="n">
-        <v>12303</v>
+        <v>12127</v>
       </c>
       <c r="I56" t="n">
         <v>12130.44168722301</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.4</v>
+        <v>-7.74</v>
       </c>
       <c r="L56" t="n">
-        <v>6.63</v>
+        <v>8.6</v>
       </c>
       <c r="M56" t="n">
         <v>0.03</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.77</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H57" t="n">
-        <v>12091</v>
+        <v>13139</v>
       </c>
       <c r="I57" t="n">
         <v>13069.61104130052</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3</v>
+        <v>-8.35</v>
       </c>
       <c r="L57" t="n">
-        <v>2.77</v>
+        <v>9.26</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>8.67</v>
       </c>
       <c r="O57" t="n">
         <v>-1.43</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>13.23</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H58" t="n">
-        <v>11641</v>
+        <v>11473</v>
       </c>
       <c r="I58" t="n">
         <v>11519.73914580273</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>-11.4</v>
+        <v>-12.68</v>
       </c>
       <c r="L58" t="n">
-        <v>11.71</v>
+        <v>13.61</v>
       </c>
       <c r="M58" t="n">
         <v>1.06</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.36</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="H59" t="n">
-        <v>11217</v>
+        <v>11413</v>
       </c>
       <c r="I59" t="n">
         <v>11296.81476968925</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K59" t="n">
-        <v>2.23</v>
+        <v>0.52</v>
       </c>
       <c r="L59" t="n">
         <v>3.25</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.4</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="H60" t="n">
-        <v>10663</v>
+        <v>10560</v>
       </c>
       <c r="I60" t="n">
         <v>10568.77376534391</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.57</v>
+        <v>-7.47</v>
       </c>
       <c r="L60" t="n">
         <v>8.880000000000001</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.06</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H61" t="n">
-        <v>9237</v>
+        <v>9970</v>
       </c>
       <c r="I61" t="n">
         <v>9847.369572074451</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>12.53</v>
+        <v>5.59</v>
       </c>
       <c r="L61" t="n">
         <v>2.19</v>
@@ -3918,7 +4649,7 @@
         <v>2.89</v>
       </c>
       <c r="N61" t="n">
-        <v>2.32</v>
+        <v>7.94</v>
       </c>
       <c r="O61" t="n">
         <v>-0.97</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>14.03</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H62" t="n">
-        <v>10940</v>
+        <v>10800</v>
       </c>
       <c r="I62" t="n">
         <v>10807.72098925111</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K62" t="n">
-        <v>9.73</v>
+        <v>8.32</v>
       </c>
       <c r="L62" t="n">
         <v>5.22</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>20</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8993,7 +9756,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.3</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -9003,7 +9766,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -9013,7 +9776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -9023,7 +9786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9033,7 +9796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -9043,7 +9806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -9083,7 +9846,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.19</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="15">
@@ -9093,7 +9856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.01</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="16">
@@ -9103,7 +9866,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="17">
@@ -9113,7 +9876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.64</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="18">
@@ -9123,7 +9886,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -9133,7 +9896,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.07</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="20">
@@ -9143,7 +9906,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.13</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="21">
@@ -9153,7 +9916,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.05</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="22">
@@ -9163,7 +9926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -9173,7 +9936,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -9183,7 +9946,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25">
@@ -9193,7 +9956,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.470000000000001</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -9203,7 +9966,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.98</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="27">
@@ -9223,7 +9986,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
